--- a/output/xlsx/ExtracaoLLT--GT-.xlsx
+++ b/output/xlsx/ExtracaoLLT--GT-.xlsx
@@ -203,7 +203,7 @@
     <t>operador: marca a opcao 'Disable LLT'</t>
   </si>
   <si>
-    <t>operador: digita um product number e serial number validos, preenche o Note e pressiona Extract</t>
+    <t>operador: digita um product number e serial number validos e pressiona Extract</t>
   </si>
   <si>
     <t>SYSTEM realiza uma extracao Disabled LLT, a envia para o servidor, e a salva nas pastas de backup local</t>
